--- a/clang-asan-x64/Running erasure.xlsx
+++ b/clang-asan-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>86.4451</v>
+        <v>35.2946</v>
       </c>
       <c r="C2" t="n">
-        <v>124.729</v>
+        <v>155.646</v>
       </c>
       <c r="D2" t="n">
-        <v>49.5287</v>
+        <v>138.383</v>
       </c>
       <c r="E2" t="n">
-        <v>22.8676</v>
+        <v>17.3362</v>
       </c>
       <c r="F2" t="n">
-        <v>39.4053</v>
+        <v>136.038</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>86.59310000000001</v>
+        <v>34.699</v>
       </c>
       <c r="C3" t="n">
-        <v>123.296</v>
+        <v>177.871</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2526</v>
+        <v>171.873</v>
       </c>
       <c r="E3" t="n">
-        <v>22.2117</v>
+        <v>16.9524</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2941</v>
+        <v>138.016</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>85.2226</v>
+        <v>34.218</v>
       </c>
       <c r="C4" t="n">
-        <v>123.148</v>
+        <v>213.724</v>
       </c>
       <c r="D4" t="n">
-        <v>49.8111</v>
+        <v>166.721</v>
       </c>
       <c r="E4" t="n">
-        <v>21.7162</v>
+        <v>16.7545</v>
       </c>
       <c r="F4" t="n">
-        <v>38.5165</v>
+        <v>157.069</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>84.1682</v>
+        <v>33.6399</v>
       </c>
       <c r="C5" t="n">
-        <v>121.823</v>
+        <v>159.952</v>
       </c>
       <c r="D5" t="n">
-        <v>50.1189</v>
+        <v>177.928</v>
       </c>
       <c r="E5" t="n">
-        <v>21.4631</v>
+        <v>16.5191</v>
       </c>
       <c r="F5" t="n">
-        <v>38.6517</v>
+        <v>137.952</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>84.3837</v>
+        <v>33.1025</v>
       </c>
       <c r="C6" t="n">
-        <v>121.741</v>
+        <v>160.385</v>
       </c>
       <c r="D6" t="n">
-        <v>49.9484</v>
+        <v>182.968</v>
       </c>
       <c r="E6" t="n">
-        <v>21.1492</v>
+        <v>16.1593</v>
       </c>
       <c r="F6" t="n">
-        <v>38.0793</v>
+        <v>138.646</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>83.9453</v>
+        <v>32.5565</v>
       </c>
       <c r="C7" t="n">
-        <v>120.537</v>
+        <v>185.005</v>
       </c>
       <c r="D7" t="n">
-        <v>51.0683</v>
+        <v>146.527</v>
       </c>
       <c r="E7" t="n">
-        <v>20.6549</v>
+        <v>15.8181</v>
       </c>
       <c r="F7" t="n">
-        <v>37.432</v>
+        <v>159.875</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>83.1002</v>
+        <v>31.8595</v>
       </c>
       <c r="C8" t="n">
-        <v>119.921</v>
+        <v>161.734</v>
       </c>
       <c r="D8" t="n">
-        <v>51.0465</v>
+        <v>177.077</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2229</v>
+        <v>15.6097</v>
       </c>
       <c r="F8" t="n">
-        <v>36.9766</v>
+        <v>165.133</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>82.1091</v>
+        <v>31.0769</v>
       </c>
       <c r="C9" t="n">
-        <v>118.649</v>
+        <v>193.003</v>
       </c>
       <c r="D9" t="n">
-        <v>51.9071</v>
+        <v>179.437</v>
       </c>
       <c r="E9" t="n">
-        <v>27.0053</v>
+        <v>22.2174</v>
       </c>
       <c r="F9" t="n">
-        <v>44.4026</v>
+        <v>147.876</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>89.8073</v>
+        <v>38.3083</v>
       </c>
       <c r="C10" t="n">
-        <v>127.014</v>
+        <v>168.749</v>
       </c>
       <c r="D10" t="n">
-        <v>51.1075</v>
+        <v>198.058</v>
       </c>
       <c r="E10" t="n">
-        <v>26.3377</v>
+        <v>21.736</v>
       </c>
       <c r="F10" t="n">
-        <v>43.8081</v>
+        <v>150.024</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>89.9851</v>
+        <v>37.9953</v>
       </c>
       <c r="C11" t="n">
-        <v>126.999</v>
+        <v>169.717</v>
       </c>
       <c r="D11" t="n">
-        <v>51.5923</v>
+        <v>152.829</v>
       </c>
       <c r="E11" t="n">
-        <v>26.1386</v>
+        <v>21.4395</v>
       </c>
       <c r="F11" t="n">
-        <v>43.59</v>
+        <v>151.952</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>89.5376</v>
+        <v>37.5404</v>
       </c>
       <c r="C12" t="n">
-        <v>125.019</v>
+        <v>171.143</v>
       </c>
       <c r="D12" t="n">
-        <v>52.767</v>
+        <v>154.299</v>
       </c>
       <c r="E12" t="n">
-        <v>25.2945</v>
+        <v>20.9727</v>
       </c>
       <c r="F12" t="n">
-        <v>43.0519</v>
+        <v>247.89</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>88.6392</v>
+        <v>37.0705</v>
       </c>
       <c r="C13" t="n">
-        <v>125.802</v>
+        <v>171.863</v>
       </c>
       <c r="D13" t="n">
-        <v>51.0993</v>
+        <v>158.268</v>
       </c>
       <c r="E13" t="n">
-        <v>25.06</v>
+        <v>20.583</v>
       </c>
       <c r="F13" t="n">
-        <v>42.2326</v>
+        <v>192.843</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>88.18389999999999</v>
+        <v>36.5715</v>
       </c>
       <c r="C14" t="n">
-        <v>126.088</v>
+        <v>173.044</v>
       </c>
       <c r="D14" t="n">
-        <v>51.023</v>
+        <v>201.116</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7036</v>
+        <v>20.1525</v>
       </c>
       <c r="F14" t="n">
-        <v>41.6305</v>
+        <v>157.13</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>87.8976</v>
+        <v>36.0196</v>
       </c>
       <c r="C15" t="n">
-        <v>122.413</v>
+        <v>175.092</v>
       </c>
       <c r="D15" t="n">
-        <v>52.3791</v>
+        <v>206.313</v>
       </c>
       <c r="E15" t="n">
-        <v>24.2014</v>
+        <v>19.7083</v>
       </c>
       <c r="F15" t="n">
-        <v>41.3296</v>
+        <v>160.078</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>87.1769</v>
+        <v>35.4651</v>
       </c>
       <c r="C16" t="n">
-        <v>122.828</v>
+        <v>177.396</v>
       </c>
       <c r="D16" t="n">
-        <v>52.4619</v>
+        <v>169.27</v>
       </c>
       <c r="E16" t="n">
-        <v>24.0877</v>
+        <v>19.3312</v>
       </c>
       <c r="F16" t="n">
-        <v>41.5404</v>
+        <v>162.761</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>86.6583</v>
+        <v>34.9477</v>
       </c>
       <c r="C17" t="n">
-        <v>123.999</v>
+        <v>179.622</v>
       </c>
       <c r="D17" t="n">
-        <v>52.0389</v>
+        <v>235.384</v>
       </c>
       <c r="E17" t="n">
-        <v>23.5856</v>
+        <v>18.9518</v>
       </c>
       <c r="F17" t="n">
-        <v>40.9023</v>
+        <v>165.919</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>85.6354</v>
+        <v>34.4296</v>
       </c>
       <c r="C18" t="n">
-        <v>123.246</v>
+        <v>220.923</v>
       </c>
       <c r="D18" t="n">
-        <v>52.4958</v>
+        <v>224.16</v>
       </c>
       <c r="E18" t="n">
-        <v>22.9833</v>
+        <v>18.6393</v>
       </c>
       <c r="F18" t="n">
-        <v>39.8422</v>
+        <v>216.333</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>85.5213</v>
+        <v>33.8826</v>
       </c>
       <c r="C19" t="n">
-        <v>121.119</v>
+        <v>185.584</v>
       </c>
       <c r="D19" t="n">
-        <v>52.5238</v>
+        <v>225.255</v>
       </c>
       <c r="E19" t="n">
-        <v>22.382</v>
+        <v>18.1807</v>
       </c>
       <c r="F19" t="n">
-        <v>39.9739</v>
+        <v>210.542</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>84.6418</v>
+        <v>33.4146</v>
       </c>
       <c r="C20" t="n">
-        <v>121.539</v>
+        <v>214.652</v>
       </c>
       <c r="D20" t="n">
-        <v>52.492</v>
+        <v>243.085</v>
       </c>
       <c r="E20" t="n">
-        <v>22.3749</v>
+        <v>17.9216</v>
       </c>
       <c r="F20" t="n">
-        <v>39.6057</v>
+        <v>216.741</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>84.0839</v>
+        <v>32.8425</v>
       </c>
       <c r="C21" t="n">
-        <v>121.726</v>
+        <v>192.818</v>
       </c>
       <c r="D21" t="n">
-        <v>55.007</v>
+        <v>190.99</v>
       </c>
       <c r="E21" t="n">
-        <v>21.5406</v>
+        <v>17.4402</v>
       </c>
       <c r="F21" t="n">
-        <v>38.4342</v>
+        <v>203.701</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>83.3141</v>
+        <v>32.1995</v>
       </c>
       <c r="C22" t="n">
-        <v>120.767</v>
+        <v>222.813</v>
       </c>
       <c r="D22" t="n">
-        <v>55.5838</v>
+        <v>194.999</v>
       </c>
       <c r="E22" t="n">
-        <v>20.9763</v>
+        <v>17.0954</v>
       </c>
       <c r="F22" t="n">
-        <v>38.1593</v>
+        <v>182.644</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>82.4893</v>
+        <v>31.4511</v>
       </c>
       <c r="C23" t="n">
-        <v>118.784</v>
+        <v>237.705</v>
       </c>
       <c r="D23" t="n">
-        <v>53.3908</v>
+        <v>198.805</v>
       </c>
       <c r="E23" t="n">
-        <v>27.371</v>
+        <v>22.6372</v>
       </c>
       <c r="F23" t="n">
-        <v>45.0289</v>
+        <v>199.625</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>90.3867</v>
+        <v>38.3908</v>
       </c>
       <c r="C24" t="n">
-        <v>127.442</v>
+        <v>199.667</v>
       </c>
       <c r="D24" t="n">
-        <v>54.8671</v>
+        <v>202.555</v>
       </c>
       <c r="E24" t="n">
-        <v>26.759</v>
+        <v>22.124</v>
       </c>
       <c r="F24" t="n">
-        <v>43.7196</v>
+        <v>203.733</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>90.029</v>
+        <v>38.0432</v>
       </c>
       <c r="C25" t="n">
-        <v>128.149</v>
+        <v>201.861</v>
       </c>
       <c r="D25" t="n">
-        <v>55.1534</v>
+        <v>207.864</v>
       </c>
       <c r="E25" t="n">
-        <v>26.419</v>
+        <v>21.6475</v>
       </c>
       <c r="F25" t="n">
-        <v>44.8894</v>
+        <v>207.235</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>89.2808</v>
+        <v>37.6101</v>
       </c>
       <c r="C26" t="n">
-        <v>126.873</v>
+        <v>203.707</v>
       </c>
       <c r="D26" t="n">
-        <v>55.1371</v>
+        <v>256.076</v>
       </c>
       <c r="E26" t="n">
-        <v>25.8948</v>
+        <v>21.2526</v>
       </c>
       <c r="F26" t="n">
-        <v>43.9947</v>
+        <v>209.706</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>89.0492</v>
+        <v>37.1334</v>
       </c>
       <c r="C27" t="n">
-        <v>126.608</v>
+        <v>206.367</v>
       </c>
       <c r="D27" t="n">
-        <v>56.3471</v>
+        <v>217.547</v>
       </c>
       <c r="E27" t="n">
-        <v>25.4809</v>
+        <v>20.7181</v>
       </c>
       <c r="F27" t="n">
-        <v>43.6189</v>
+        <v>214.551</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>88.4023</v>
+        <v>36.6563</v>
       </c>
       <c r="C28" t="n">
-        <v>126.188</v>
+        <v>208.44</v>
       </c>
       <c r="D28" t="n">
-        <v>52.2337</v>
+        <v>236.1</v>
       </c>
       <c r="E28" t="n">
-        <v>24.9122</v>
+        <v>20.2856</v>
       </c>
       <c r="F28" t="n">
-        <v>41.7953</v>
+        <v>218.42</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>87.9542</v>
+        <v>36.1437</v>
       </c>
       <c r="C29" t="n">
-        <v>125.146</v>
+        <v>211.699</v>
       </c>
       <c r="D29" t="n">
-        <v>55.3393</v>
+        <v>306.91</v>
       </c>
       <c r="E29" t="n">
-        <v>24.5177</v>
+        <v>19.9537</v>
       </c>
       <c r="F29" t="n">
-        <v>43.4117</v>
+        <v>222.512</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>87.0408</v>
+        <v>35.5991</v>
       </c>
       <c r="C30" t="n">
-        <v>124.48</v>
+        <v>215.206</v>
       </c>
       <c r="D30" t="n">
-        <v>57.3512</v>
+        <v>309.804</v>
       </c>
       <c r="E30" t="n">
-        <v>24.0098</v>
+        <v>19.5576</v>
       </c>
       <c r="F30" t="n">
-        <v>41.0724</v>
+        <v>227.618</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>86.33799999999999</v>
+        <v>35.0418</v>
       </c>
       <c r="C31" t="n">
-        <v>124.044</v>
+        <v>218.713</v>
       </c>
       <c r="D31" t="n">
-        <v>55.7383</v>
+        <v>236.954</v>
       </c>
       <c r="E31" t="n">
-        <v>23.5424</v>
+        <v>19.2609</v>
       </c>
       <c r="F31" t="n">
-        <v>42.1275</v>
+        <v>230.983</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>86.1536</v>
+        <v>34.5479</v>
       </c>
       <c r="C32" t="n">
-        <v>123.544</v>
+        <v>223.65</v>
       </c>
       <c r="D32" t="n">
-        <v>56.5413</v>
+        <v>365.224</v>
       </c>
       <c r="E32" t="n">
-        <v>23.2356</v>
+        <v>18.8368</v>
       </c>
       <c r="F32" t="n">
-        <v>40.1568</v>
+        <v>236.335</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>85.66030000000001</v>
+        <v>34.0361</v>
       </c>
       <c r="C33" t="n">
-        <v>125.642</v>
+        <v>313.489</v>
       </c>
       <c r="D33" t="n">
-        <v>55.4948</v>
+        <v>246.475</v>
       </c>
       <c r="E33" t="n">
-        <v>22.6798</v>
+        <v>18.4493</v>
       </c>
       <c r="F33" t="n">
-        <v>40.3544</v>
+        <v>271.937</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>84.94459999999999</v>
+        <v>33.5056</v>
       </c>
       <c r="C34" t="n">
-        <v>123.72</v>
+        <v>233.744</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5559</v>
+        <v>358.042</v>
       </c>
       <c r="E34" t="n">
-        <v>22.2421</v>
+        <v>18.0653</v>
       </c>
       <c r="F34" t="n">
-        <v>41.4854</v>
+        <v>321.598</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>84.2794</v>
+        <v>32.9526</v>
       </c>
       <c r="C35" t="n">
-        <v>125.124</v>
+        <v>273.482</v>
       </c>
       <c r="D35" t="n">
-        <v>61.9436</v>
+        <v>250.794</v>
       </c>
       <c r="E35" t="n">
-        <v>21.7705</v>
+        <v>17.6914</v>
       </c>
       <c r="F35" t="n">
-        <v>41.4389</v>
+        <v>248.805</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>83.5732</v>
+        <v>32.3447</v>
       </c>
       <c r="C36" t="n">
-        <v>122.84</v>
+        <v>270.855</v>
       </c>
       <c r="D36" t="n">
-        <v>61.4872</v>
+        <v>254.197</v>
       </c>
       <c r="E36" t="n">
-        <v>21.3076</v>
+        <v>17.3146</v>
       </c>
       <c r="F36" t="n">
-        <v>39.1588</v>
+        <v>295.518</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>82.7957</v>
+        <v>31.6412</v>
       </c>
       <c r="C37" t="n">
-        <v>118.88</v>
+        <v>290.711</v>
       </c>
       <c r="D37" t="n">
-        <v>61.4097</v>
+        <v>259.208</v>
       </c>
       <c r="E37" t="n">
-        <v>27.4852</v>
+        <v>22.7514</v>
       </c>
       <c r="F37" t="n">
-        <v>49.4803</v>
+        <v>276.75</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>90.1216</v>
+        <v>38.172</v>
       </c>
       <c r="C38" t="n">
-        <v>128.395</v>
+        <v>232.877</v>
       </c>
       <c r="D38" t="n">
-        <v>62.3781</v>
+        <v>263.484</v>
       </c>
       <c r="E38" t="n">
-        <v>27.0055</v>
+        <v>22.2473</v>
       </c>
       <c r="F38" t="n">
-        <v>44.7948</v>
+        <v>278.88</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>89.9639</v>
+        <v>37.8857</v>
       </c>
       <c r="C39" t="n">
-        <v>128.928</v>
+        <v>234.384</v>
       </c>
       <c r="D39" t="n">
-        <v>60.0624</v>
+        <v>266.712</v>
       </c>
       <c r="E39" t="n">
-        <v>26.4479</v>
+        <v>21.8127</v>
       </c>
       <c r="F39" t="n">
-        <v>44.3881</v>
+        <v>281.702</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>89.5074</v>
+        <v>37.5132</v>
       </c>
       <c r="C40" t="n">
-        <v>134.951</v>
+        <v>236.899</v>
       </c>
       <c r="D40" t="n">
-        <v>61.0518</v>
+        <v>301.63</v>
       </c>
       <c r="E40" t="n">
-        <v>25.9293</v>
+        <v>21.3471</v>
       </c>
       <c r="F40" t="n">
-        <v>43.3978</v>
+        <v>285.156</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>88.78579999999999</v>
+        <v>37.0676</v>
       </c>
       <c r="C41" t="n">
-        <v>127.747</v>
+        <v>239.061</v>
       </c>
       <c r="D41" t="n">
-        <v>61.9046</v>
+        <v>274.548</v>
       </c>
       <c r="E41" t="n">
-        <v>25.371</v>
+        <v>20.9095</v>
       </c>
       <c r="F41" t="n">
-        <v>43.0058</v>
+        <v>285.607</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>88.54949999999999</v>
+        <v>36.605</v>
       </c>
       <c r="C42" t="n">
-        <v>126.947</v>
+        <v>241.836</v>
       </c>
       <c r="D42" t="n">
-        <v>59.8995</v>
+        <v>374.115</v>
       </c>
       <c r="E42" t="n">
-        <v>25.1034</v>
+        <v>20.4734</v>
       </c>
       <c r="F42" t="n">
-        <v>42.2677</v>
+        <v>286.197</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>87.9547</v>
+        <v>36.084</v>
       </c>
       <c r="C43" t="n">
-        <v>127.416</v>
+        <v>245.204</v>
       </c>
       <c r="D43" t="n">
-        <v>65.3437</v>
+        <v>358.385</v>
       </c>
       <c r="E43" t="n">
-        <v>24.6774</v>
+        <v>20.1136</v>
       </c>
       <c r="F43" t="n">
-        <v>43.0406</v>
+        <v>286.442</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>87.069</v>
+        <v>35.5503</v>
       </c>
       <c r="C44" t="n">
-        <v>127.622</v>
+        <v>250.049</v>
       </c>
       <c r="D44" t="n">
-        <v>61.29</v>
+        <v>358.927</v>
       </c>
       <c r="E44" t="n">
-        <v>24.2534</v>
+        <v>19.6862</v>
       </c>
       <c r="F44" t="n">
-        <v>42.6011</v>
+        <v>287.887</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>86.7441</v>
+        <v>35.015</v>
       </c>
       <c r="C45" t="n">
-        <v>130.324</v>
+        <v>253.092</v>
       </c>
       <c r="D45" t="n">
-        <v>60.5607</v>
+        <v>307.03</v>
       </c>
       <c r="E45" t="n">
-        <v>23.788</v>
+        <v>19.2945</v>
       </c>
       <c r="F45" t="n">
-        <v>40.7226</v>
+        <v>287.376</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>86.21769999999999</v>
+        <v>34.508</v>
       </c>
       <c r="C46" t="n">
-        <v>129.238</v>
+        <v>255.862</v>
       </c>
       <c r="D46" t="n">
-        <v>65.30289999999999</v>
+        <v>356.708</v>
       </c>
       <c r="E46" t="n">
-        <v>23.2617</v>
+        <v>18.9163</v>
       </c>
       <c r="F46" t="n">
-        <v>41.5883</v>
+        <v>286.995</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>85.5774</v>
+        <v>33.9484</v>
       </c>
       <c r="C47" t="n">
-        <v>125.56</v>
+        <v>281.554</v>
       </c>
       <c r="D47" t="n">
-        <v>63.0092</v>
+        <v>364.174</v>
       </c>
       <c r="E47" t="n">
-        <v>22.8591</v>
+        <v>18.4812</v>
       </c>
       <c r="F47" t="n">
-        <v>41.1374</v>
+        <v>287.043</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>84.5215</v>
+        <v>33.4424</v>
       </c>
       <c r="C48" t="n">
-        <v>131.665</v>
+        <v>266.998</v>
       </c>
       <c r="D48" t="n">
-        <v>60.4321</v>
+        <v>371.266</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3182</v>
+        <v>18.1135</v>
       </c>
       <c r="F48" t="n">
-        <v>42.8778</v>
+        <v>286.005</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>84.181</v>
+        <v>32.8984</v>
       </c>
       <c r="C49" t="n">
-        <v>128.462</v>
+        <v>271.415</v>
       </c>
       <c r="D49" t="n">
-        <v>65.2179</v>
+        <v>320.309</v>
       </c>
       <c r="E49" t="n">
-        <v>21.842</v>
+        <v>17.7263</v>
       </c>
       <c r="F49" t="n">
-        <v>40.2234</v>
+        <v>286.264</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>83.4158</v>
+        <v>32.3356</v>
       </c>
       <c r="C50" t="n">
-        <v>125.748</v>
+        <v>277.432</v>
       </c>
       <c r="D50" t="n">
-        <v>79.13039999999999</v>
+        <v>376.345</v>
       </c>
       <c r="E50" t="n">
-        <v>21.4537</v>
+        <v>17.3526</v>
       </c>
       <c r="F50" t="n">
-        <v>38.5529</v>
+        <v>289.316</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>82.5016</v>
+        <v>31.6606</v>
       </c>
       <c r="C51" t="n">
-        <v>127.73</v>
+        <v>302.681</v>
       </c>
       <c r="D51" t="n">
-        <v>75.5827</v>
+        <v>298.206</v>
       </c>
       <c r="E51" t="n">
-        <v>27.0398</v>
+        <v>23.3691</v>
       </c>
       <c r="F51" t="n">
-        <v>47.799</v>
+        <v>304.959</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>81.9683</v>
+        <v>30.9628</v>
       </c>
       <c r="C52" t="n">
-        <v>123.676</v>
+        <v>287.64</v>
       </c>
       <c r="D52" t="n">
-        <v>75.9521</v>
+        <v>364.394</v>
       </c>
       <c r="E52" t="n">
-        <v>26.5398</v>
+        <v>22.7859</v>
       </c>
       <c r="F52" t="n">
-        <v>45.2577</v>
+        <v>324.397</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>90.12569999999999</v>
+        <v>38.0783</v>
       </c>
       <c r="C53" t="n">
-        <v>135.573</v>
+        <v>253.522</v>
       </c>
       <c r="D53" t="n">
-        <v>68.2719</v>
+        <v>447.263</v>
       </c>
       <c r="E53" t="n">
-        <v>26.213</v>
+        <v>22.2358</v>
       </c>
       <c r="F53" t="n">
-        <v>44.8686</v>
+        <v>301.063</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>89.40900000000001</v>
+        <v>37.7381</v>
       </c>
       <c r="C54" t="n">
-        <v>135.836</v>
+        <v>293.559</v>
       </c>
       <c r="D54" t="n">
-        <v>76.6217</v>
+        <v>303.522</v>
       </c>
       <c r="E54" t="n">
-        <v>25.5564</v>
+        <v>21.6562</v>
       </c>
       <c r="F54" t="n">
-        <v>43.4777</v>
+        <v>299.475</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>89.07340000000001</v>
+        <v>37.3041</v>
       </c>
       <c r="C55" t="n">
-        <v>126.341</v>
+        <v>252.069</v>
       </c>
       <c r="D55" t="n">
-        <v>80.62649999999999</v>
+        <v>371.214</v>
       </c>
       <c r="E55" t="n">
-        <v>25.1806</v>
+        <v>21.1364</v>
       </c>
       <c r="F55" t="n">
-        <v>42.9038</v>
+        <v>300.282</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>88.499</v>
+        <v>36.7947</v>
       </c>
       <c r="C56" t="n">
-        <v>125.893</v>
+        <v>245.804</v>
       </c>
       <c r="D56" t="n">
-        <v>78.9586</v>
+        <v>327.612</v>
       </c>
       <c r="E56" t="n">
-        <v>24.7153</v>
+        <v>20.7403</v>
       </c>
       <c r="F56" t="n">
-        <v>44.0015</v>
+        <v>298.067</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>87.8434</v>
+        <v>36.2811</v>
       </c>
       <c r="C57" t="n">
-        <v>137.784</v>
+        <v>255.672</v>
       </c>
       <c r="D57" t="n">
-        <v>74.8477</v>
+        <v>325.011</v>
       </c>
       <c r="E57" t="n">
-        <v>24.3584</v>
+        <v>20.3079</v>
       </c>
       <c r="F57" t="n">
-        <v>44.2817</v>
+        <v>374.144</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>87.3009</v>
+        <v>35.7289</v>
       </c>
       <c r="C58" t="n">
-        <v>136.953</v>
+        <v>257.669</v>
       </c>
       <c r="D58" t="n">
-        <v>72.30719999999999</v>
+        <v>395.532</v>
       </c>
       <c r="E58" t="n">
-        <v>23.9072</v>
+        <v>19.8831</v>
       </c>
       <c r="F58" t="n">
-        <v>42.1978</v>
+        <v>293.441</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>87.0031</v>
+        <v>35.1985</v>
       </c>
       <c r="C59" t="n">
-        <v>136.358</v>
+        <v>261.04</v>
       </c>
       <c r="D59" t="n">
-        <v>65.2599</v>
+        <v>313.537</v>
       </c>
       <c r="E59" t="n">
-        <v>23.5829</v>
+        <v>19.4723</v>
       </c>
       <c r="F59" t="n">
-        <v>41.2424</v>
+        <v>292.712</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>86.12</v>
+        <v>34.6965</v>
       </c>
       <c r="C60" t="n">
-        <v>136.478</v>
+        <v>262.734</v>
       </c>
       <c r="D60" t="n">
-        <v>80.2997</v>
+        <v>450.845</v>
       </c>
       <c r="E60" t="n">
-        <v>23.1611</v>
+        <v>19.0286</v>
       </c>
       <c r="F60" t="n">
-        <v>40.7334</v>
+        <v>291.94</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>85.3437</v>
+        <v>34.1701</v>
       </c>
       <c r="C61" t="n">
-        <v>136.536</v>
+        <v>340.007</v>
       </c>
       <c r="D61" t="n">
-        <v>76.07089999999999</v>
+        <v>353.807</v>
       </c>
       <c r="E61" t="n">
-        <v>22.7539</v>
+        <v>18.6423</v>
       </c>
       <c r="F61" t="n">
-        <v>40.4844</v>
+        <v>294.055</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>85.0873</v>
+        <v>33.6572</v>
       </c>
       <c r="C62" t="n">
-        <v>137.295</v>
+        <v>270.927</v>
       </c>
       <c r="D62" t="n">
-        <v>68.91889999999999</v>
+        <v>407.284</v>
       </c>
       <c r="E62" t="n">
-        <v>22.3707</v>
+        <v>18.2747</v>
       </c>
       <c r="F62" t="n">
-        <v>43.791</v>
+        <v>304.652</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>84.11020000000001</v>
+        <v>33.115</v>
       </c>
       <c r="C63" t="n">
-        <v>122.255</v>
+        <v>276.783</v>
       </c>
       <c r="D63" t="n">
-        <v>74.9157</v>
+        <v>414.284</v>
       </c>
       <c r="E63" t="n">
-        <v>21.9636</v>
+        <v>17.9038</v>
       </c>
       <c r="F63" t="n">
-        <v>40.9145</v>
+        <v>359.624</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>83.6498</v>
+        <v>32.5465</v>
       </c>
       <c r="C64" t="n">
-        <v>136.3</v>
+        <v>346.303</v>
       </c>
       <c r="D64" t="n">
-        <v>97.29430000000001</v>
+        <v>318.024</v>
       </c>
       <c r="E64" t="n">
-        <v>21.5138</v>
+        <v>17.4868</v>
       </c>
       <c r="F64" t="n">
-        <v>38.9271</v>
+        <v>285.14</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>82.86490000000001</v>
+        <v>31.9274</v>
       </c>
       <c r="C65" t="n">
-        <v>136.879</v>
+        <v>283.954</v>
       </c>
       <c r="D65" t="n">
-        <v>90.8321</v>
+        <v>318.529</v>
       </c>
       <c r="E65" t="n">
-        <v>21.137</v>
+        <v>17.0425</v>
       </c>
       <c r="F65" t="n">
-        <v>38.3948</v>
+        <v>282.197</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>81.7594</v>
+        <v>31.1947</v>
       </c>
       <c r="C66" t="n">
-        <v>135.663</v>
+        <v>298.919</v>
       </c>
       <c r="D66" t="n">
-        <v>91.54389999999999</v>
+        <v>393.942</v>
       </c>
       <c r="E66" t="n">
-        <v>27.1752</v>
+        <v>23.3899</v>
       </c>
       <c r="F66" t="n">
-        <v>44.8036</v>
+        <v>302.589</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>90.1575</v>
+        <v>38.1949</v>
       </c>
       <c r="C67" t="n">
-        <v>142.292</v>
+        <v>252.776</v>
       </c>
       <c r="D67" t="n">
-        <v>82.28319999999999</v>
+        <v>375.909</v>
       </c>
       <c r="E67" t="n">
-        <v>26.5259</v>
+        <v>22.7051</v>
       </c>
       <c r="F67" t="n">
-        <v>44.9217</v>
+        <v>303.977</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>89.7667</v>
+        <v>37.8546</v>
       </c>
       <c r="C68" t="n">
-        <v>138.345</v>
+        <v>252.825</v>
       </c>
       <c r="D68" t="n">
-        <v>88.2938</v>
+        <v>340.808</v>
       </c>
       <c r="E68" t="n">
-        <v>26.1123</v>
+        <v>22.0995</v>
       </c>
       <c r="F68" t="n">
-        <v>43.8468</v>
+        <v>301.699</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>89.0951</v>
+        <v>37.427</v>
       </c>
       <c r="C69" t="n">
-        <v>144.678</v>
+        <v>254.17</v>
       </c>
       <c r="D69" t="n">
-        <v>89.8746</v>
+        <v>396.268</v>
       </c>
       <c r="E69" t="n">
-        <v>25.5324</v>
+        <v>21.5273</v>
       </c>
       <c r="F69" t="n">
-        <v>43.3335</v>
+        <v>299.207</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>88.8523</v>
+        <v>36.9332</v>
       </c>
       <c r="C70" t="n">
-        <v>144.303</v>
+        <v>255.234</v>
       </c>
       <c r="D70" t="n">
-        <v>87.1807</v>
+        <v>371.757</v>
       </c>
       <c r="E70" t="n">
-        <v>25.1612</v>
+        <v>21.0292</v>
       </c>
       <c r="F70" t="n">
-        <v>46.8068</v>
+        <v>299.776</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>88.26260000000001</v>
+        <v>36.4355</v>
       </c>
       <c r="C71" t="n">
-        <v>141.905</v>
+        <v>256.563</v>
       </c>
       <c r="D71" t="n">
-        <v>72.735</v>
+        <v>367.71</v>
       </c>
       <c r="E71" t="n">
-        <v>24.5568</v>
+        <v>20.4579</v>
       </c>
       <c r="F71" t="n">
-        <v>43.5162</v>
+        <v>295.874</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>87.9438</v>
+        <v>35.9067</v>
       </c>
       <c r="C72" t="n">
-        <v>125.174</v>
+        <v>258.897</v>
       </c>
       <c r="D72" t="n">
-        <v>71.8034</v>
+        <v>419.737</v>
       </c>
       <c r="E72" t="n">
-        <v>24.0501</v>
+        <v>19.9746</v>
       </c>
       <c r="F72" t="n">
-        <v>42.6208</v>
+        <v>295.065</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>86.8326</v>
+        <v>35.3626</v>
       </c>
       <c r="C73" t="n">
-        <v>130.685</v>
+        <v>289.41</v>
       </c>
       <c r="D73" t="n">
-        <v>88.5489</v>
+        <v>466.537</v>
       </c>
       <c r="E73" t="n">
-        <v>23.6565</v>
+        <v>19.502</v>
       </c>
       <c r="F73" t="n">
-        <v>41.6165</v>
+        <v>293.341</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>86.3566</v>
+        <v>34.8266</v>
       </c>
       <c r="C74" t="n">
-        <v>148.232</v>
+        <v>280.49</v>
       </c>
       <c r="D74" t="n">
-        <v>92.7149</v>
+        <v>462.395</v>
       </c>
       <c r="E74" t="n">
-        <v>23.2895</v>
+        <v>19.1175</v>
       </c>
       <c r="F74" t="n">
-        <v>41.0084</v>
+        <v>342.057</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>85.6683</v>
+        <v>34.3152</v>
       </c>
       <c r="C75" t="n">
-        <v>146.184</v>
+        <v>308.524</v>
       </c>
       <c r="D75" t="n">
-        <v>90.066</v>
+        <v>345.912</v>
       </c>
       <c r="E75" t="n">
-        <v>22.8484</v>
+        <v>18.6733</v>
       </c>
       <c r="F75" t="n">
-        <v>40.4308</v>
+        <v>292.446</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>85.122</v>
+        <v>33.791</v>
       </c>
       <c r="C76" t="n">
-        <v>143.606</v>
+        <v>270.11</v>
       </c>
       <c r="D76" t="n">
-        <v>81.3954</v>
+        <v>332.703</v>
       </c>
       <c r="E76" t="n">
-        <v>22.4521</v>
+        <v>18.3591</v>
       </c>
       <c r="F76" t="n">
-        <v>41.2877</v>
+        <v>291.424</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>84.45959999999999</v>
+        <v>33.2465</v>
       </c>
       <c r="C77" t="n">
-        <v>150.21</v>
+        <v>344.813</v>
       </c>
       <c r="D77" t="n">
-        <v>77.7308</v>
+        <v>386.151</v>
       </c>
       <c r="E77" t="n">
-        <v>22.0833</v>
+        <v>17.9782</v>
       </c>
       <c r="F77" t="n">
-        <v>39.662</v>
+        <v>287.752</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>84.0441</v>
+        <v>32.6732</v>
       </c>
       <c r="C78" t="n">
-        <v>139.42</v>
+        <v>295.04</v>
       </c>
       <c r="D78" t="n">
-        <v>102.62</v>
+        <v>327.105</v>
       </c>
       <c r="E78" t="n">
-        <v>21.6399</v>
+        <v>17.6047</v>
       </c>
       <c r="F78" t="n">
-        <v>39.1258</v>
+        <v>332.256</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>82.8419</v>
+        <v>32.0519</v>
       </c>
       <c r="C79" t="n">
-        <v>141.493</v>
+        <v>361.487</v>
       </c>
       <c r="D79" t="n">
-        <v>95.7379</v>
+        <v>345.103</v>
       </c>
       <c r="E79" t="n">
-        <v>21.2405</v>
+        <v>17.1305</v>
       </c>
       <c r="F79" t="n">
-        <v>38.4773</v>
+        <v>282.819</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>82.00449999999999</v>
+        <v>31.3986</v>
       </c>
       <c r="C80" t="n">
-        <v>144.52</v>
+        <v>289.635</v>
       </c>
       <c r="D80" t="n">
-        <v>97.4161</v>
+        <v>422.406</v>
       </c>
       <c r="E80" t="n">
-        <v>26.914</v>
+        <v>22.7715</v>
       </c>
       <c r="F80" t="n">
-        <v>44.8397</v>
+        <v>307.263</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>90.3556</v>
+        <v>38.3619</v>
       </c>
       <c r="C81" t="n">
-        <v>150.398</v>
+        <v>322.929</v>
       </c>
       <c r="D81" t="n">
-        <v>97.0324</v>
+        <v>330.149</v>
       </c>
       <c r="E81" t="n">
-        <v>26.3139</v>
+        <v>22.2167</v>
       </c>
       <c r="F81" t="n">
-        <v>44.1629</v>
+        <v>303.767</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>90.2427</v>
+        <v>38.0049</v>
       </c>
       <c r="C82" t="n">
-        <v>146.638</v>
+        <v>253.321</v>
       </c>
       <c r="D82" t="n">
-        <v>95.5917</v>
+        <v>391.904</v>
       </c>
       <c r="E82" t="n">
-        <v>25.8865</v>
+        <v>21.7692</v>
       </c>
       <c r="F82" t="n">
-        <v>43.7278</v>
+        <v>301.213</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>89.7773</v>
+        <v>37.602</v>
       </c>
       <c r="C83" t="n">
-        <v>149.57</v>
+        <v>254.053</v>
       </c>
       <c r="D83" t="n">
-        <v>82.8475</v>
+        <v>393.097</v>
       </c>
       <c r="E83" t="n">
-        <v>25.4566</v>
+        <v>21.286</v>
       </c>
       <c r="F83" t="n">
-        <v>43.7031</v>
+        <v>301.477</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>89.6623</v>
+        <v>37.1194</v>
       </c>
       <c r="C84" t="n">
-        <v>150.571</v>
+        <v>294.743</v>
       </c>
       <c r="D84" t="n">
-        <v>81.4049</v>
+        <v>397.606</v>
       </c>
       <c r="E84" t="n">
-        <v>24.9149</v>
+        <v>20.7667</v>
       </c>
       <c r="F84" t="n">
-        <v>42.6893</v>
+        <v>328.479</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>88.5539</v>
+        <v>36.6028</v>
       </c>
       <c r="C85" t="n">
-        <v>149.282</v>
+        <v>300.274</v>
       </c>
       <c r="D85" t="n">
-        <v>79.8419</v>
+        <v>460.283</v>
       </c>
       <c r="E85" t="n">
-        <v>24.5379</v>
+        <v>20.3431</v>
       </c>
       <c r="F85" t="n">
-        <v>42.3054</v>
+        <v>322.384</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>87.6892</v>
+        <v>36.0757</v>
       </c>
       <c r="C86" t="n">
-        <v>150.104</v>
+        <v>260.002</v>
       </c>
       <c r="D86" t="n">
-        <v>99.50530000000001</v>
+        <v>383.585</v>
       </c>
       <c r="E86" t="n">
-        <v>24.2673</v>
+        <v>19.916</v>
       </c>
       <c r="F86" t="n">
-        <v>42.3965</v>
+        <v>326.564</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>87.10250000000001</v>
+        <v>35.5369</v>
       </c>
       <c r="C87" t="n">
-        <v>149.921</v>
+        <v>307.133</v>
       </c>
       <c r="D87" t="n">
-        <v>105.674</v>
+        <v>351.308</v>
       </c>
       <c r="E87" t="n">
-        <v>23.8039</v>
+        <v>19.5279</v>
       </c>
       <c r="F87" t="n">
-        <v>41.5768</v>
+        <v>325.942</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>86.6151</v>
+        <v>34.9876</v>
       </c>
       <c r="C88" t="n">
-        <v>154.983</v>
+        <v>337.518</v>
       </c>
       <c r="D88" t="n">
-        <v>101.447</v>
+        <v>498.938</v>
       </c>
       <c r="E88" t="n">
-        <v>23.4246</v>
+        <v>19.1049</v>
       </c>
       <c r="F88" t="n">
-        <v>40.7935</v>
+        <v>336.258</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>85.8805</v>
+        <v>34.4716</v>
       </c>
       <c r="C89" t="n">
-        <v>148.565</v>
+        <v>267.562</v>
       </c>
       <c r="D89" t="n">
-        <v>92.2749</v>
+        <v>507.87</v>
       </c>
       <c r="E89" t="n">
-        <v>22.9928</v>
+        <v>18.7534</v>
       </c>
       <c r="F89" t="n">
-        <v>40.427</v>
+        <v>317.302</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>85.2269</v>
+        <v>33.9463</v>
       </c>
       <c r="C90" t="n">
-        <v>121.599</v>
+        <v>322.31</v>
       </c>
       <c r="D90" t="n">
-        <v>86.13330000000001</v>
+        <v>390.505</v>
       </c>
       <c r="E90" t="n">
-        <v>22.6016</v>
+        <v>18.3905</v>
       </c>
       <c r="F90" t="n">
-        <v>40.1272</v>
+        <v>291.111</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>84.76990000000001</v>
+        <v>33.4211</v>
       </c>
       <c r="C91" t="n">
-        <v>123.737</v>
+        <v>272.45</v>
       </c>
       <c r="D91" t="n">
-        <v>86.99469999999999</v>
+        <v>353.188</v>
       </c>
       <c r="E91" t="n">
-        <v>22.2475</v>
+        <v>17.986</v>
       </c>
       <c r="F91" t="n">
-        <v>39.8855</v>
+        <v>288.092</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>84.0133</v>
+        <v>32.8566</v>
       </c>
       <c r="C92" t="n">
-        <v>119.732</v>
+        <v>276.808</v>
       </c>
       <c r="D92" t="n">
-        <v>95.7773</v>
+        <v>327.667</v>
       </c>
       <c r="E92" t="n">
-        <v>21.8485</v>
+        <v>17.6008</v>
       </c>
       <c r="F92" t="n">
-        <v>39.1291</v>
+        <v>326.434</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>83.21639999999999</v>
+        <v>32.2431</v>
       </c>
       <c r="C93" t="n">
-        <v>118.624</v>
+        <v>357.622</v>
       </c>
       <c r="D93" t="n">
-        <v>90.40949999999999</v>
+        <v>361.326</v>
       </c>
       <c r="E93" t="n">
-        <v>21.4256</v>
+        <v>17.3064</v>
       </c>
       <c r="F93" t="n">
-        <v>38.6287</v>
+        <v>282.983</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>82.3335</v>
+        <v>31.5569</v>
       </c>
       <c r="C94" t="n">
-        <v>149.531</v>
+        <v>288.515</v>
       </c>
       <c r="D94" t="n">
-        <v>92.12649999999999</v>
+        <v>367.64</v>
       </c>
       <c r="E94" t="n">
-        <v>27.0803</v>
+        <v>22.8193</v>
       </c>
       <c r="F94" t="n">
-        <v>44.6572</v>
+        <v>306.619</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>90.80419999999999</v>
+        <v>38.403</v>
       </c>
       <c r="C95" t="n">
-        <v>173.968</v>
+        <v>252.724</v>
       </c>
       <c r="D95" t="n">
-        <v>88.40940000000001</v>
+        <v>460.943</v>
       </c>
       <c r="E95" t="n">
-        <v>26.6066</v>
+        <v>22.308</v>
       </c>
       <c r="F95" t="n">
-        <v>44.2164</v>
+        <v>303.878</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>90.1097</v>
+        <v>38.0584</v>
       </c>
       <c r="C96" t="n">
-        <v>141.379</v>
+        <v>253.382</v>
       </c>
       <c r="D96" t="n">
-        <v>88.7017</v>
+        <v>443.906</v>
       </c>
       <c r="E96" t="n">
-        <v>26.029</v>
+        <v>21.7952</v>
       </c>
       <c r="F96" t="n">
-        <v>43.8045</v>
+        <v>302.887</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>89.616</v>
+        <v>37.6585</v>
       </c>
       <c r="C97" t="n">
-        <v>159.13</v>
+        <v>254.226</v>
       </c>
       <c r="D97" t="n">
-        <v>81.4717</v>
+        <v>329.614</v>
       </c>
       <c r="E97" t="n">
-        <v>25.4879</v>
+        <v>21.3515</v>
       </c>
       <c r="F97" t="n">
-        <v>43.1965</v>
+        <v>300.565</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>88.9842</v>
+        <v>37.2136</v>
       </c>
       <c r="C98" t="n">
-        <v>157.796</v>
+        <v>255.263</v>
       </c>
       <c r="D98" t="n">
-        <v>80.5185</v>
+        <v>368.468</v>
       </c>
       <c r="E98" t="n">
-        <v>25.0889</v>
+        <v>20.8763</v>
       </c>
       <c r="F98" t="n">
-        <v>42.6532</v>
+        <v>298.884</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>88.2175</v>
+        <v>36.715</v>
       </c>
       <c r="C99" t="n">
-        <v>152.964</v>
+        <v>256.424</v>
       </c>
       <c r="D99" t="n">
-        <v>83.7385</v>
+        <v>367.006</v>
       </c>
       <c r="E99" t="n">
-        <v>24.6615</v>
+        <v>20.449</v>
       </c>
       <c r="F99" t="n">
-        <v>42.2509</v>
+        <v>297.569</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>87.74169999999999</v>
+        <v>36.1939</v>
       </c>
       <c r="C100" t="n">
-        <v>158.112</v>
+        <v>257.713</v>
       </c>
       <c r="D100" t="n">
-        <v>77.7394</v>
+        <v>391.652</v>
       </c>
       <c r="E100" t="n">
-        <v>24.3721</v>
+        <v>20.0702</v>
       </c>
       <c r="F100" t="n">
-        <v>41.7406</v>
+        <v>296.13</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>86.6797</v>
+        <v>35.6545</v>
       </c>
       <c r="C101" t="n">
-        <v>165.894</v>
+        <v>286.072</v>
       </c>
       <c r="D101" t="n">
-        <v>90.5117</v>
+        <v>423.439</v>
       </c>
       <c r="E101" t="n">
-        <v>23.9506</v>
+        <v>19.6705</v>
       </c>
       <c r="F101" t="n">
-        <v>41.279</v>
+        <v>295.052</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>86.35550000000001</v>
+        <v>35.1117</v>
       </c>
       <c r="C102" t="n">
-        <v>152.28</v>
+        <v>263.404</v>
       </c>
       <c r="D102" t="n">
-        <v>78.4218</v>
+        <v>369.914</v>
       </c>
       <c r="E102" t="n">
-        <v>23.5314</v>
+        <v>19.2184</v>
       </c>
       <c r="F102" t="n">
-        <v>40.9598</v>
+        <v>318.896</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>85.6493</v>
+        <v>34.5837</v>
       </c>
       <c r="C103" t="n">
-        <v>152.454</v>
+        <v>320.291</v>
       </c>
       <c r="D103" t="n">
-        <v>79.7124</v>
+        <v>335.632</v>
       </c>
       <c r="E103" t="n">
-        <v>23.1437</v>
+        <v>18.8919</v>
       </c>
       <c r="F103" t="n">
-        <v>40.3277</v>
+        <v>290.695</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>84.6767</v>
+        <v>34.0564</v>
       </c>
       <c r="C104" t="n">
-        <v>157.371</v>
+        <v>356.854</v>
       </c>
       <c r="D104" t="n">
-        <v>72.93300000000001</v>
+        <v>344.507</v>
       </c>
       <c r="E104" t="n">
-        <v>22.7385</v>
+        <v>18.524</v>
       </c>
       <c r="F104" t="n">
-        <v>40.1315</v>
+        <v>303.765</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>84.614</v>
+        <v>33.5219</v>
       </c>
       <c r="C105" t="n">
-        <v>152.247</v>
+        <v>274.725</v>
       </c>
       <c r="D105" t="n">
-        <v>68.2619</v>
+        <v>352.909</v>
       </c>
       <c r="E105" t="n">
-        <v>22.4032</v>
+        <v>18.1495</v>
       </c>
       <c r="F105" t="n">
-        <v>39.4638</v>
+        <v>324.333</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>83.9824</v>
+        <v>32.9646</v>
       </c>
       <c r="C106" t="n">
-        <v>163.808</v>
+        <v>273.047</v>
       </c>
       <c r="D106" t="n">
-        <v>81.34350000000001</v>
+        <v>337.455</v>
       </c>
       <c r="E106" t="n">
-        <v>22.0174</v>
+        <v>17.7614</v>
       </c>
       <c r="F106" t="n">
-        <v>39.0322</v>
+        <v>285.38</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>83.21259999999999</v>
+        <v>32.3732</v>
       </c>
       <c r="C107" t="n">
-        <v>152.218</v>
+        <v>307.069</v>
       </c>
       <c r="D107" t="n">
-        <v>85.6456</v>
+        <v>330.035</v>
       </c>
       <c r="E107" t="n">
-        <v>21.629</v>
+        <v>17.3816</v>
       </c>
       <c r="F107" t="n">
-        <v>38.6195</v>
+        <v>306.208</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>82.30759999999999</v>
+        <v>31.7035</v>
       </c>
       <c r="C108" t="n">
-        <v>156.177</v>
+        <v>287.722</v>
       </c>
       <c r="D108" t="n">
-        <v>90.59399999999999</v>
+        <v>414.714</v>
       </c>
       <c r="E108" t="n">
-        <v>27.2867</v>
+        <v>22.9711</v>
       </c>
       <c r="F108" t="n">
-        <v>44.776</v>
+        <v>306.606</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>81.34139999999999</v>
+        <v>30.9263</v>
       </c>
       <c r="C109" t="n">
-        <v>161.106</v>
+        <v>290.666</v>
       </c>
       <c r="D109" t="n">
-        <v>85.5132</v>
+        <v>412.541</v>
       </c>
       <c r="E109" t="n">
-        <v>26.7523</v>
+        <v>22.4097</v>
       </c>
       <c r="F109" t="n">
-        <v>44.3164</v>
+        <v>305.32</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>89.76439999999999</v>
+        <v>38.1421</v>
       </c>
       <c r="C110" t="n">
-        <v>156.963</v>
+        <v>254.977</v>
       </c>
       <c r="D110" t="n">
-        <v>91.1567</v>
+        <v>458.704</v>
       </c>
       <c r="E110" t="n">
-        <v>26.2635</v>
+        <v>21.9232</v>
       </c>
       <c r="F110" t="n">
-        <v>43.761</v>
+        <v>304.177</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>89.8926</v>
+        <v>37.7612</v>
       </c>
       <c r="C111" t="n">
-        <v>162.597</v>
+        <v>254.95</v>
       </c>
       <c r="D111" t="n">
-        <v>76.9933</v>
+        <v>403.801</v>
       </c>
       <c r="E111" t="n">
-        <v>25.7675</v>
+        <v>21.4023</v>
       </c>
       <c r="F111" t="n">
-        <v>43.5208</v>
+        <v>302.012</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.6164</v>
+        <v>37.3078</v>
       </c>
       <c r="C112" t="n">
-        <v>172.036</v>
+        <v>318.256</v>
       </c>
       <c r="D112" t="n">
-        <v>82.2312</v>
+        <v>403.568</v>
       </c>
       <c r="E112" t="n">
-        <v>25.3512</v>
+        <v>20.895</v>
       </c>
       <c r="F112" t="n">
-        <v>43.186</v>
+        <v>300.661</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>88.559</v>
+        <v>36.8158</v>
       </c>
       <c r="C113" t="n">
-        <v>189.407</v>
+        <v>257.513</v>
       </c>
       <c r="D113" t="n">
-        <v>73.5804</v>
+        <v>389.227</v>
       </c>
       <c r="E113" t="n">
-        <v>24.8787</v>
+        <v>20.5427</v>
       </c>
       <c r="F113" t="n">
-        <v>42.6892</v>
+        <v>299.008</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>87.9796</v>
+        <v>36.2945</v>
       </c>
       <c r="C114" t="n">
-        <v>179.471</v>
+        <v>305.774</v>
       </c>
       <c r="D114" t="n">
-        <v>74.742</v>
+        <v>366.184</v>
       </c>
       <c r="E114" t="n">
-        <v>24.4662</v>
+        <v>20.1195</v>
       </c>
       <c r="F114" t="n">
-        <v>42.0877</v>
+        <v>359.545</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>87.42319999999999</v>
+        <v>35.7623</v>
       </c>
       <c r="C115" t="n">
-        <v>187.93</v>
+        <v>292.248</v>
       </c>
       <c r="D115" t="n">
-        <v>73.7259</v>
+        <v>346.552</v>
       </c>
       <c r="E115" t="n">
-        <v>23.987</v>
+        <v>19.7141</v>
       </c>
       <c r="F115" t="n">
-        <v>41.4585</v>
+        <v>341.715</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>87.30629999999999</v>
+        <v>35.2272</v>
       </c>
       <c r="C116" t="n">
-        <v>183.209</v>
+        <v>278.961</v>
       </c>
       <c r="D116" t="n">
-        <v>69.3665</v>
+        <v>334.902</v>
       </c>
       <c r="E116" t="n">
-        <v>23.5784</v>
+        <v>19.3349</v>
       </c>
       <c r="F116" t="n">
-        <v>41.0821</v>
+        <v>323.422</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>86.155</v>
+        <v>34.7028</v>
       </c>
       <c r="C117" t="n">
-        <v>203.88</v>
+        <v>265.691</v>
       </c>
       <c r="D117" t="n">
-        <v>69.2266</v>
+        <v>384.792</v>
       </c>
       <c r="E117" t="n">
-        <v>23.2131</v>
+        <v>19.0059</v>
       </c>
       <c r="F117" t="n">
-        <v>40.6126</v>
+        <v>302.217</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>85.5971</v>
+        <v>34.1814</v>
       </c>
       <c r="C118" t="n">
-        <v>191.594</v>
+        <v>266.273</v>
       </c>
       <c r="D118" t="n">
-        <v>66.6557</v>
+        <v>381.617</v>
       </c>
       <c r="E118" t="n">
-        <v>22.7606</v>
+        <v>18.6215</v>
       </c>
       <c r="F118" t="n">
-        <v>40.1325</v>
+        <v>290.459</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>84.8985</v>
+        <v>33.6514</v>
       </c>
       <c r="C119" t="n">
-        <v>180.542</v>
+        <v>269.759</v>
       </c>
       <c r="D119" t="n">
-        <v>66.21769999999999</v>
+        <v>382.729</v>
       </c>
       <c r="E119" t="n">
-        <v>22.4004</v>
+        <v>18.2394</v>
       </c>
       <c r="F119" t="n">
-        <v>39.7898</v>
+        <v>288.767</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>84.051</v>
+        <v>33.1155</v>
       </c>
       <c r="C120" t="n">
-        <v>189.317</v>
+        <v>273.014</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7029</v>
+        <v>385.269</v>
       </c>
       <c r="E120" t="n">
-        <v>22.0286</v>
+        <v>17.8583</v>
       </c>
       <c r="F120" t="n">
-        <v>39.2677</v>
+        <v>287.225</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>83.2814</v>
+        <v>32.5185</v>
       </c>
       <c r="C121" t="n">
-        <v>192.873</v>
+        <v>325.95</v>
       </c>
       <c r="D121" t="n">
-        <v>86.3951</v>
+        <v>395.339</v>
       </c>
       <c r="E121" t="n">
-        <v>21.6688</v>
+        <v>17.4737</v>
       </c>
       <c r="F121" t="n">
-        <v>38.7577</v>
+        <v>285.478</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>82.4823</v>
+        <v>31.8584</v>
       </c>
       <c r="C122" t="n">
-        <v>201.227</v>
+        <v>325.896</v>
       </c>
       <c r="D122" t="n">
-        <v>85.6178</v>
+        <v>386.047</v>
       </c>
       <c r="E122" t="n">
-        <v>21.2648</v>
+        <v>17.0979</v>
       </c>
       <c r="F122" t="n">
-        <v>38.219</v>
+        <v>334.258</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>81.5239</v>
+        <v>31.088</v>
       </c>
       <c r="C123" t="n">
-        <v>192.707</v>
+        <v>332.003</v>
       </c>
       <c r="D123" t="n">
-        <v>133.854</v>
+        <v>375.505</v>
       </c>
       <c r="E123" t="n">
-        <v>26.6973</v>
+        <v>22.4328</v>
       </c>
       <c r="F123" t="n">
-        <v>44.4254</v>
+        <v>335.829</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>90.6707</v>
+        <v>38.2273</v>
       </c>
       <c r="C124" t="n">
-        <v>208.005</v>
+        <v>254.258</v>
       </c>
       <c r="D124" t="n">
-        <v>80.4301</v>
+        <v>365.812</v>
       </c>
       <c r="E124" t="n">
-        <v>26.2105</v>
+        <v>21.9479</v>
       </c>
       <c r="F124" t="n">
-        <v>43.8924</v>
+        <v>328.466</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>89.9402</v>
+        <v>37.8563</v>
       </c>
       <c r="C125" t="n">
-        <v>210.413</v>
+        <v>255.374</v>
       </c>
       <c r="D125" t="n">
-        <v>78.883</v>
+        <v>354.683</v>
       </c>
       <c r="E125" t="n">
-        <v>25.8792</v>
+        <v>21.488</v>
       </c>
       <c r="F125" t="n">
-        <v>43.3435</v>
+        <v>317.061</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>89.4087</v>
+        <v>37.416</v>
       </c>
       <c r="C126" t="n">
-        <v>210.451</v>
+        <v>255.99</v>
       </c>
       <c r="D126" t="n">
-        <v>78.7384</v>
+        <v>344.096</v>
       </c>
       <c r="E126" t="n">
-        <v>25.3429</v>
+        <v>21.0318</v>
       </c>
       <c r="F126" t="n">
-        <v>42.9297</v>
+        <v>302.705</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>88.7427</v>
+        <v>36.9198</v>
       </c>
       <c r="C127" t="n">
-        <v>213.202</v>
+        <v>256.002</v>
       </c>
       <c r="D127" t="n">
-        <v>75.6503</v>
+        <v>334.97</v>
       </c>
       <c r="E127" t="n">
-        <v>24.9034</v>
+        <v>20.4897</v>
       </c>
       <c r="F127" t="n">
-        <v>42.4049</v>
+        <v>301.146</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>87.9119</v>
+        <v>36.3884</v>
       </c>
       <c r="C128" t="n">
-        <v>213.543</v>
+        <v>260.367</v>
       </c>
       <c r="D128" t="n">
-        <v>77.4041</v>
+        <v>362.963</v>
       </c>
       <c r="E128" t="n">
-        <v>24.4744</v>
+        <v>20.1311</v>
       </c>
       <c r="F128" t="n">
-        <v>41.9354</v>
+        <v>300.012</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>87.2552</v>
+        <v>35.8527</v>
       </c>
       <c r="C129" t="n">
-        <v>214.352</v>
+        <v>260.734</v>
       </c>
       <c r="D129" t="n">
-        <v>87.7606</v>
+        <v>362.284</v>
       </c>
       <c r="E129" t="n">
-        <v>24.0757</v>
+        <v>19.7225</v>
       </c>
       <c r="F129" t="n">
-        <v>41.6562</v>
+        <v>298.633</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>86.63200000000001</v>
+        <v>35.3251</v>
       </c>
       <c r="C130" t="n">
-        <v>195.306</v>
+        <v>259.962</v>
       </c>
       <c r="D130" t="n">
-        <v>91.8883</v>
+        <v>392.806</v>
       </c>
       <c r="E130" t="n">
-        <v>23.7045</v>
+        <v>19.347</v>
       </c>
       <c r="F130" t="n">
-        <v>41.2005</v>
+        <v>296.151</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>85.8413</v>
+        <v>34.7891</v>
       </c>
       <c r="C131" t="n">
-        <v>192.489</v>
+        <v>262.784</v>
       </c>
       <c r="D131" t="n">
-        <v>93.815</v>
+        <v>391.304</v>
       </c>
       <c r="E131" t="n">
-        <v>23.2839</v>
+        <v>18.9169</v>
       </c>
       <c r="F131" t="n">
-        <v>40.7328</v>
+        <v>296.587</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>85.2723</v>
+        <v>34.2648</v>
       </c>
       <c r="C132" t="n">
-        <v>189.033</v>
+        <v>297.354</v>
       </c>
       <c r="D132" t="n">
-        <v>83.4229</v>
+        <v>418.778</v>
       </c>
       <c r="E132" t="n">
-        <v>22.927</v>
+        <v>18.5777</v>
       </c>
       <c r="F132" t="n">
-        <v>40.1842</v>
+        <v>329.444</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>84.7192</v>
+        <v>33.7434</v>
       </c>
       <c r="C133" t="n">
-        <v>191.832</v>
+        <v>300.281</v>
       </c>
       <c r="D133" t="n">
-        <v>82.4901</v>
+        <v>419.547</v>
       </c>
       <c r="E133" t="n">
-        <v>22.5203</v>
+        <v>18.2397</v>
       </c>
       <c r="F133" t="n">
-        <v>39.6642</v>
+        <v>326.584</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.41160000000001</v>
+        <v>33.1997</v>
       </c>
       <c r="C134" t="n">
-        <v>191.117</v>
+        <v>333.661</v>
       </c>
       <c r="D134" t="n">
-        <v>86.086</v>
+        <v>427.322</v>
       </c>
       <c r="E134" t="n">
-        <v>22.1071</v>
+        <v>17.9511</v>
       </c>
       <c r="F134" t="n">
-        <v>39.3302</v>
+        <v>324.268</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.3746</v>
+        <v>32.631</v>
       </c>
       <c r="C135" t="n">
-        <v>207.828</v>
+        <v>335.378</v>
       </c>
       <c r="D135" t="n">
-        <v>99.3385</v>
+        <v>440.358</v>
       </c>
       <c r="E135" t="n">
-        <v>21.7246</v>
+        <v>17.5525</v>
       </c>
       <c r="F135" t="n">
-        <v>39.0591</v>
+        <v>351.731</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>82.7321</v>
+        <v>31.9718</v>
       </c>
       <c r="C136" t="n">
-        <v>207.571</v>
+        <v>337.049</v>
       </c>
       <c r="D136" t="n">
-        <v>108.595</v>
+        <v>436.557</v>
       </c>
       <c r="E136" t="n">
-        <v>21.3397</v>
+        <v>17.1607</v>
       </c>
       <c r="F136" t="n">
-        <v>38.3347</v>
+        <v>348.309</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>81.9909</v>
+        <v>31.2532</v>
       </c>
       <c r="C137" t="n">
-        <v>204.114</v>
+        <v>368.638</v>
       </c>
       <c r="D137" t="n">
-        <v>94.7501</v>
+        <v>430.686</v>
       </c>
       <c r="E137" t="n">
-        <v>26.8522</v>
+        <v>22.6219</v>
       </c>
       <c r="F137" t="n">
-        <v>44.7179</v>
+        <v>398.839</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>121.972</v>
+        <v>38.2907</v>
       </c>
       <c r="C138" t="n">
-        <v>209.156</v>
+        <v>341.525</v>
       </c>
       <c r="D138" t="n">
-        <v>130.42</v>
+        <v>421.185</v>
       </c>
       <c r="E138" t="n">
-        <v>26.3422</v>
+        <v>22.086</v>
       </c>
       <c r="F138" t="n">
-        <v>44.2901</v>
+        <v>394.753</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>118.347</v>
+        <v>37.9282</v>
       </c>
       <c r="C139" t="n">
-        <v>203.724</v>
+        <v>337.782</v>
       </c>
       <c r="D139" t="n">
-        <v>120.371</v>
+        <v>418.375</v>
       </c>
       <c r="E139" t="n">
-        <v>25.9196</v>
+        <v>21.6085</v>
       </c>
       <c r="F139" t="n">
-        <v>43.6069</v>
+        <v>389.052</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>115.441</v>
+        <v>37.504</v>
       </c>
       <c r="C140" t="n">
-        <v>203.816</v>
+        <v>334.075</v>
       </c>
       <c r="D140" t="n">
-        <v>100.665</v>
+        <v>434.721</v>
       </c>
       <c r="E140" t="n">
-        <v>25.4661</v>
+        <v>21.1198</v>
       </c>
       <c r="F140" t="n">
-        <v>43.2305</v>
+        <v>382.789</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>114.437</v>
+        <v>37.0301</v>
       </c>
       <c r="C141" t="n">
-        <v>226.932</v>
+        <v>332.458</v>
       </c>
       <c r="D141" t="n">
-        <v>93.7718</v>
+        <v>432.053</v>
       </c>
       <c r="E141" t="n">
-        <v>25.0159</v>
+        <v>20.6866</v>
       </c>
       <c r="F141" t="n">
-        <v>42.64</v>
+        <v>374.709</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>119.074</v>
+        <v>36.5146</v>
       </c>
       <c r="C142" t="n">
-        <v>210.736</v>
+        <v>338.552</v>
       </c>
       <c r="D142" t="n">
-        <v>93.77849999999999</v>
+        <v>430.129</v>
       </c>
       <c r="E142" t="n">
-        <v>24.5904</v>
+        <v>20.2303</v>
       </c>
       <c r="F142" t="n">
-        <v>42.4904</v>
+        <v>388.12</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>120.056</v>
+        <v>35.9954</v>
       </c>
       <c r="C143" t="n">
-        <v>203.499</v>
+        <v>337.115</v>
       </c>
       <c r="D143" t="n">
-        <v>88.28279999999999</v>
+        <v>427.843</v>
       </c>
       <c r="E143" t="n">
-        <v>24.1671</v>
+        <v>19.8518</v>
       </c>
       <c r="F143" t="n">
-        <v>41.783</v>
+        <v>382.7</v>
       </c>
     </row>
   </sheetData>
